--- a/docs/downloads/经营分_河南省区__河南北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南北片区_2026-10-18.xlsx
@@ -713,7 +713,7 @@
         <v>70</v>
       </c>
       <c r="I2" t="n">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -946,22 +946,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新乡市</t>
+          <t>安阳市</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7632273815859955722</t>
+          <t>7522006205410052136</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(新乡人民公园胖东来大胖店)</t>
+          <t>维也纳酒店(安阳东站光明路店)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(新乡人民公园胖东来大胖店)</t>
+          <t>维也纳酒店(安阳高铁站迎宾公园店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -973,11 +973,11 @@
         <v>75</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -987,13 +987,13 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
@@ -1005,7 +1005,7 @@
         <v>30</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
         <v>20</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>安阳市</t>
+          <t>新乡市</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7522006205410052136</t>
+          <t>7632273815859955722</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>维也纳酒店(安阳东站光明路店)</t>
+          <t>白玉兰商务酒店(新乡人民公园胖东来大胖店)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>维也纳酒店(安阳高铁站迎宾公园店)</t>
+          <t>白玉兰商务酒店(新乡人民公园胖东来大胖店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1058,14 +1058,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1075,13 +1075,13 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
         <v>30</v>
@@ -1093,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
         <v>20</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1215,33 +1215,33 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601155218145019911</t>
+          <t>7268152524715067444</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>麗枫酒店(安阳中国文字博物馆店)​</t>
+          <t>派酒店（安阳师范学院店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>麗枫酒店(安阳中国文字博物馆店)</t>
+          <t>派·酒店(安阳师范学院店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1251,19 +1251,19 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7268152524715067444</t>
+          <t>7603620817825433606</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>派酒店（安阳师范学院店）</t>
+          <t>锦江之星（安阳殷墟博物馆中州路店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>派·酒店(安阳师范学院店)</t>
+          <t>锦江之星(安阳殷墟博物馆中州路店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1339,19 +1339,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>安阳市</t>
+          <t>新乡市</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7603620817825433606</t>
+          <t>7438105207977805878</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>锦江之星（安阳殷墟博物馆中州路店）</t>
+          <t>锦江之星（新乡延津西街公园酒店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>锦江之星(安阳殷墟博物馆中州路店)</t>
+          <t>锦江之星(新乡延津西街公园店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1427,19 +1427,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="n">
         <v>15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>20</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1474,22 +1474,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新乡市</t>
+          <t>安阳市</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7438105207977805878</t>
+          <t>6601155218145019911</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>锦江之星（新乡延津西街公园酒店）</t>
+          <t>麗枫酒店(安阳中国文字博物馆店)​</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>锦江之星(新乡延津西街公园店)</t>
+          <t>麗枫酒店(安阳中国文字博物馆店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7316030916717971519</t>
+          <t>7224326547908331576</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>喆啡锐品酒店（安阳高铁站吾悦广场店）</t>
+          <t>维也纳国际酒店（5.0版安阳CBD公园万达广场店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>喆啡锐品酒店(安阳高铁站吾悦广场店)</t>
+          <t>维也纳国际酒店(5.0版安阳CBD万达广场店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1586,42 +1586,42 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,附加分,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="n">
         <v>20</v>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7224326547908331576</t>
+          <t>7316030916717971519</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版安阳CBD公园万达广场店）</t>
+          <t>喆啡锐品酒店（安阳高铁站吾悦广场店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(5.0版安阳CBD万达广场店)</t>
+          <t>喆啡锐品酒店(安阳高铁站吾悦广场店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1674,42 +1674,42 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,附加分,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T13" t="n">
         <v>20</v>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601267913242445827</t>
+          <t>7236215714678310964</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7天优品（安阳汤阴岳飞庙景区店）</t>
+          <t>锦江之星品尚（安阳幼师酒店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7天优品(安阳汤阴岳飞庙景区店)</t>
+          <t>锦江之星品尚酒店(安阳安汤新城店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2043,19 +2043,19 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2095,17 +2095,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7236639673269880887</t>
+          <t>6601267913242445827</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7天优品（安阳火车站殷墟博物馆店）</t>
+          <t>7天优品（安阳汤阴岳飞庙景区店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7天优品酒店(安阳火车站殷墟博物馆店)</t>
+          <t>7天优品(安阳汤阴岳飞庙景区店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6601141093620779022</t>
+          <t>7236639673269880887</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>锦江之星（安阳殷墟博物馆火车站店）</t>
+          <t>7天优品（安阳火车站殷墟博物馆店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>锦江之星酒店(安阳火车站店)</t>
+          <t>7天优品酒店(安阳火车站殷墟博物馆店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2219,7 +2219,7 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -2231,7 +2231,7 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6601254861700859908</t>
+          <t>6601141093620779022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>喆啡酒店（安阳文字博物馆店）</t>
+          <t>锦江之星（安阳殷墟博物馆火车站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>喆啡酒店(安阳文字博物馆店)</t>
+          <t>锦江之星酒店(安阳火车站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2319,7 +2319,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2359,17 +2359,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7053019605333182495</t>
+          <t>6601254861700859908</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(安阳汤阴上亿广场店)</t>
+          <t>喆啡酒店（安阳文字博物馆店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(汤阴上亿广场店)</t>
+          <t>喆啡酒店(安阳文字博物馆店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2381,7 +2381,7 @@
         <v>97</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2447,17 +2447,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7236215714678310964</t>
+          <t>7053019605333182495</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>锦江之星品尚（安阳幼师酒店）</t>
+          <t>维也纳国际酒店(安阳汤阴上亿广场店)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>锦江之星品尚酒店(安阳安汤新城店)</t>
+          <t>维也纳国际酒店(汤阴上亿广场店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2469,11 +2469,11 @@
         <v>97</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -3613,7 +3613,7 @@
         <v>105</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>105</v>
       </c>
       <c r="I36" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H39" t="n">
